--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2023_magallanes_y_la_antartica_chilena.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2023_magallanes_y_la_antartica_chilena.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>25.00137551581843</v>
+      </c>
+      <c r="C2">
         <v>33.67922971114168</v>
-      </c>
-      <c r="C2">
-        <v>25.00137551581843</v>
       </c>
       <c r="D2">
         <v>2.969189047899105</v>
       </c>
       <c r="E2">
-        <v>21.22454074520981</v>
+        <v>15.75578532742491</v>
       </c>
       <c r="F2">
         <v>63.01967392736527</v>
       </c>
       <c r="G2">
-        <v>15.75578532742491</v>
+        <v>21.22454074520981</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>28.03738317757009</v>
+      </c>
+      <c r="C3">
         <v>40.18691588785047</v>
-      </c>
-      <c r="C3">
-        <v>28.03738317757009</v>
       </c>
       <c r="D3">
         <v>2.488372093023256</v>
       </c>
       <c r="E3">
-        <v>23.88888888888889</v>
+        <v>16.66666666666666</v>
       </c>
       <c r="F3">
         <v>59.44444444444445</v>
       </c>
       <c r="G3">
-        <v>16.66666666666666</v>
+        <v>23.88888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>9.433962264150944</v>
+      </c>
+      <c r="C4">
         <v>25.47169811320755</v>
-      </c>
-      <c r="C4">
-        <v>9.433962264150944</v>
       </c>
       <c r="D4">
         <v>3.925925925925926</v>
       </c>
       <c r="E4">
-        <v>18.88111888111888</v>
+        <v>6.993006993006993</v>
       </c>
       <c r="F4">
         <v>74.12587412587413</v>
       </c>
       <c r="G4">
-        <v>6.993006993006993</v>
+        <v>18.88111888111888</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>23.68421052631579</v>
+      </c>
+      <c r="C5">
         <v>32.23684210526316</v>
-      </c>
-      <c r="C5">
-        <v>23.68421052631579</v>
       </c>
       <c r="D5">
         <v>3.102040816326531</v>
       </c>
       <c r="E5">
-        <v>20.67510548523207</v>
+        <v>15.18987341772152</v>
       </c>
       <c r="F5">
         <v>64.13502109704642</v>
       </c>
       <c r="G5">
-        <v>15.18987341772152</v>
+        <v>20.67510548523207</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>35.40885221305327</v>
+      </c>
+      <c r="C6">
         <v>14.32858214553638</v>
-      </c>
-      <c r="C6">
-        <v>35.40885221305327</v>
       </c>
       <c r="D6">
         <v>6.979057591623037</v>
       </c>
       <c r="E6">
-        <v>9.569138276553105</v>
+        <v>23.64729458917836</v>
       </c>
       <c r="F6">
-        <v>66.78356713426852</v>
+        <v>66.78356713426854</v>
       </c>
       <c r="G6">
-        <v>23.64729458917835</v>
+        <v>9.569138276553106</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>26.11373434613016</v>
+      </c>
+      <c r="C7">
         <v>27.59187025251488</v>
-      </c>
-      <c r="C7">
-        <v>26.11373434613016</v>
       </c>
       <c r="D7">
         <v>3.624255952380953</v>
       </c>
       <c r="E7">
-        <v>17.95111526646187</v>
+        <v>16.98944837718712</v>
       </c>
       <c r="F7">
         <v>65.05943635635101</v>
       </c>
       <c r="G7">
-        <v>16.98944837718712</v>
+        <v>17.95111526646187</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>37.83783783783784</v>
+      </c>
+      <c r="C8">
         <v>34.83483483483483</v>
-      </c>
-      <c r="C8">
-        <v>37.83783783783784</v>
       </c>
       <c r="D8">
         <v>2.870689655172414</v>
       </c>
       <c r="E8">
-        <v>20.17391304347826</v>
+        <v>21.91304347826087</v>
       </c>
       <c r="F8">
         <v>57.91304347826087</v>
       </c>
       <c r="G8">
-        <v>21.91304347826087</v>
+        <v>20.17391304347826</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>34.44444444444444</v>
+      </c>
+      <c r="C9">
         <v>30</v>
-      </c>
-      <c r="C9">
-        <v>34.44444444444444</v>
       </c>
       <c r="D9">
         <v>3.333333333333333</v>
       </c>
       <c r="E9">
-        <v>18.24324324324324</v>
+        <v>20.94594594594594</v>
       </c>
       <c r="F9">
         <v>60.81081081081081</v>
       </c>
       <c r="G9">
-        <v>20.94594594594594</v>
+        <v>18.24324324324324</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>24.26354133671207</v>
+      </c>
+      <c r="C10">
         <v>30.17104846373139</v>
-      </c>
-      <c r="C10">
-        <v>24.26354133671207</v>
       </c>
       <c r="D10">
         <v>3.314435695538058</v>
       </c>
       <c r="E10">
-        <v>19.53645779920008</v>
+        <v>15.71120910675828</v>
       </c>
       <c r="F10">
         <v>64.75233309404163</v>
       </c>
       <c r="G10">
-        <v>15.71120910675828</v>
+        <v>19.53645779920008</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>10.36585365853658</v>
+      </c>
+      <c r="C11">
         <v>13.41463414634146</v>
-      </c>
-      <c r="C11">
-        <v>10.36585365853658</v>
       </c>
       <c r="D11">
         <v>7.454545454545454</v>
       </c>
       <c r="E11">
-        <v>10.83743842364532</v>
+        <v>8.374384236453201</v>
       </c>
       <c r="F11">
         <v>80.78817733990148</v>
       </c>
       <c r="G11">
-        <v>8.374384236453201</v>
+        <v>10.83743842364532</v>
       </c>
     </row>
   </sheetData>
